--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a470284\Mine\Projects\k8s-rightsizer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729977BA-5423-48CB-A8C1-640FD6874E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDF267D-81EA-4723-8F26-C8AD62DA3994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HCO-Container Recommendatio DU'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HCO-Container Recommendatio DU'!$A$1:$N$2</definedName>
     <definedName name="APM">'[1]APM Export'!$A$1:$L$10550</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Environment</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>POD</t>
   </si>
   <si>
     <t>Container</t>
@@ -523,27 +520,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875B3D47-7E8A-4A9A-9CCE-2B38D6005361}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.59765625" style="5" customWidth="1"/>
-    <col min="2" max="3" width="42.296875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="29.296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.3984375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.09765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.09765625" style="5"/>
-    <col min="8" max="8" width="24" style="5" customWidth="1"/>
-    <col min="9" max="9" width="21.8984375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="38" style="5" customWidth="1"/>
-    <col min="11" max="11" width="33.8984375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="21" style="5" customWidth="1"/>
-    <col min="13" max="13" width="18.3984375" style="5" customWidth="1"/>
-    <col min="14" max="14" width="34.59765625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="32.296875" style="5" customWidth="1"/>
-    <col min="16" max="16384" width="9.09765625" style="2"/>
+    <col min="2" max="2" width="42.296875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="29.296875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="28.3984375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.09765625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="5"/>
+    <col min="7" max="7" width="24" style="5" customWidth="1"/>
+    <col min="8" max="8" width="21.8984375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="38" style="5" customWidth="1"/>
+    <col min="10" max="10" width="33.8984375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="21" style="5" customWidth="1"/>
+    <col min="12" max="12" width="18.3984375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="34.59765625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="32.296875" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,10 +548,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -574,11 +571,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>11</v>
@@ -586,60 +583,56 @@
       <c r="N1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>17</v>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2</v>
       </c>
       <c r="G2" s="3">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="H2" s="3">
         <v>500</v>
       </c>
       <c r="I2" s="3">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J2" s="3">
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>50</v>
+        <v>2048</v>
       </c>
       <c r="L2" s="3">
         <v>2048</v>
       </c>
       <c r="M2" s="3">
-        <v>2048</v>
+        <v>200</v>
       </c>
       <c r="N2" s="3">
-        <v>200</v>
-      </c>
-      <c r="O2" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O2" xr:uid="{875B3D47-7E8A-4A9A-9CCE-2B38D6005361}"/>
+  <autoFilter ref="A1:N2" xr:uid="{875B3D47-7E8A-4A9A-9CCE-2B38D6005361}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -649,12 +642,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A9D9B79EAD5BA94E9A3F379047946D7F" ma:contentTypeVersion="6" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="7e4e56769a6e72cb5ab09fe359caccfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e9d8133e-f311-40cb-b671-5c6149caa565" xmlns:ns3="8762e784-f5b5-458b-8d6e-f5b044ec62de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="36c6d8eefc5e52647de0e841ad48104e" ns2:_="" ns3:_="">
     <xsd:import namespace="e9d8133e-f311-40cb-b671-5c6149caa565"/>
@@ -831,6 +818,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -841,23 +834,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8BD82F-AA6D-48FD-8510-6ED9BD04899D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8762e784-f5b5-458b-8d6e-f5b044ec62de"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="e9d8133e-f311-40cb-b671-5c6149caa565"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB5485A-4DB0-46AA-854B-F0993EB63B4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -876,6 +852,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8BD82F-AA6D-48FD-8510-6ED9BD04899D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8762e784-f5b5-458b-8d6e-f5b044ec62de"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="e9d8133e-f311-40cb-b671-5c6149caa565"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0BB01DB-2273-48CA-9212-17EA76FB34AA}">
   <ds:schemaRefs>
